--- a/results/Int All Data -0.7/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.7/Rando_1_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8203974609282891</v>
+        <v>0.8117915923903304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8203974609282891</v>
+        <v>0.8080627788310084</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8184850456976316</v>
+        <v>0.808123520368222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8198409779010214</v>
+        <v>0.808123520368222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8191630117993265</v>
+        <v>0.8119992831744056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8191630117993265</v>
+        <v>0.8075925035133886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8195019948501741</v>
+        <v>0.8072535204625412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8195019948501741</v>
+        <v>0.807531761976175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8149129905775161</v>
+        <v>0.8085487111287173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8163296643181197</v>
+        <v>0.8083312111522971</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8136785414485537</v>
+        <v>0.8064442620940739</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8136785414485537</v>
+        <v>0.8055840713807382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8187280118464861</v>
+        <v>0.8061405544080058</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8193707025834017</v>
+        <v>0.8078707450270224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8219061901662846</v>
+        <v>0.7962591135885611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8219061901662846</v>
+        <v>0.796658838176622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8199232242060686</v>
+        <v>0.8030995161427237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8199232242060686</v>
+        <v>0.8024822915782425</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8129456815973892</v>
+        <v>0.801065617837639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8129456815973892</v>
+        <v>0.7987534780189205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8125106816445489</v>
+        <v>0.7984144949680729</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8083821434971656</v>
+        <v>0.7984144949680729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8074866774190506</v>
+        <v>0.7984144949680729</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8088171434500062</v>
+        <v>0.8045161898833273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8152578214161079</v>
+        <v>0.8034384991935712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8169527366703451</v>
+        <v>0.8031602576799374</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8132846646482367</v>
+        <v>0.8034384991935712</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8083821434971656</v>
+        <v>0.8024215500410288</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8076434358582572</v>
+        <v>0.8024215500410288</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8103553002650368</v>
+        <v>0.804698414494968</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8143270799732134</v>
+        <v>0.8077492619525952</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8169233090933099</v>
+        <v>0.8082097280778699</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.817914792073418</v>
+        <v>0.8040557237580526</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8230250040085643</v>
+        <v>0.8056291559378626</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8293089235354594</v>
+        <v>0.8056291559378626</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8304218895899946</v>
+        <v>0.80596813898871</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8335687539496147</v>
+        <v>0.8056291559378626</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8351323769370796</v>
+        <v>0.8063071220395575</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8337764447336898</v>
+        <v>0.8041517406600455</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8353498769134999</v>
+        <v>0.8044907237108929</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8367665506541033</v>
+        <v>0.8023960838685945</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8536451524669175</v>
+        <v>0.8030995161427237</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8552793261839413</v>
+        <v>0.8020218254529679</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8571368476651293</v>
+        <v>0.8019003423785405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8545719325052111</v>
+        <v>0.8007619101515708</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8533629495486827</v>
+        <v>0.8003014440262962</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8509038604831027</v>
+        <v>0.8013183931788386</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.849461720570065</v>
+        <v>0.8020571008177471</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8422470596002753</v>
+        <v>0.8040302575856182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8517542420040936</v>
+        <v>0.8054469313262216</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8515720173924526</v>
+        <v>0.8057859143770691</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8554281618139461</v>
+        <v>0.8052039651773673</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8481174839421635</v>
+        <v>0.8070458296784659</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8481527593069429</v>
+        <v>0.8080020372937947</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8457700687586656</v>
+        <v>0.8060288805259237</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8405030983843128</v>
+        <v>0.8038734991464116</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8398858738198316</v>
+        <v>0.8035345160955643</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8411203229487941</v>
+        <v>0.8002661686615169</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8422332890033295</v>
+        <v>0.7963805966629882</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8297007253143186</v>
+        <v>0.7970585627646831</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8297007253143186</v>
+        <v>0.7954596644124388</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8379832677815191</v>
+        <v>0.7927125246408797</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8320911500334833</v>
+        <v>0.7929300246173</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8320304084962697</v>
+        <v>0.7930515076917273</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8357435650755025</v>
+        <v>0.7916955754883375</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8354653235618686</v>
+        <v>0.7903396432849477</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8341603237033474</v>
+        <v>0.7903396432849477</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8319343915942767</v>
+        <v>0.7928594738877414</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8321420823783519</v>
+        <v>0.7882253850579591</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8327593069428332</v>
+        <v>0.7897988172377692</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8314033747394434</v>
+        <v>0.7918679909076333</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8135900700791339</v>
+        <v>0.7912253001707177</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8183809173481226</v>
+        <v>0.7927889231581826</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8149107269177442</v>
+        <v>0.7912507663431519</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8125633117342463</v>
+        <v>0.7912507663431519</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8109134810371335</v>
+        <v>0.7731279062090302</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8242024843665997</v>
+        <v>0.7731279062090302</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8116836912745348</v>
+        <v>0.7731279062090302</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.815643775407223</v>
+        <v>0.7665148128236325</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8172524829518124</v>
+        <v>0.7718778000999783</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8172524829518124</v>
+        <v>0.7705375248766777</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.830635428161814</v>
+        <v>0.7674866774190505</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.835048055610575</v>
+        <v>0.755283287588542</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8366567631551645</v>
+        <v>0.7516152155664337</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8412359582354771</v>
+        <v>0.7463835205568603</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8372896446997349</v>
+        <v>0.7463835205568603</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8350088188411948</v>
+        <v>0.7505120587042434</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8352361280099601</v>
+        <v>0.7408030333040945</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8349578864963263</v>
+        <v>0.7380558935325354</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8369761278213218</v>
+        <v>0.7395685841751318</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8354692849664695</v>
+        <v>0.738116635069749</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8368252171698594</v>
+        <v>0.7562845797609952</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8382673570828971</v>
+        <v>0.7519130754647576</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8334608528338191</v>
+        <v>0.7436559991699914</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8239085858728766</v>
+        <v>0.7393452364109674</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8205638399215265</v>
+        <v>0.7376855965215094</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8187240504418852</v>
+        <v>0.7372858719334483</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8138058723107251</v>
+        <v>0.7338960414249738</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8138058723107251</v>
+        <v>0.7344525244522415</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7999428425907587</v>
+        <v>0.7251334144478085</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8026547069975383</v>
+        <v>0.7170938381294625</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8009147071861766</v>
+        <v>0.713122058421286</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8009147071861766</v>
+        <v>0.6891542401177103</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7894598341869217</v>
+        <v>0.6989494732275072</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7820120162606228</v>
+        <v>0.662980108089754</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7805346009828056</v>
+        <v>0.662980108089754</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8022000886600078</v>
+        <v>0.6685919093026984</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8081959574809239</v>
+        <v>0.6694873753808136</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8043103854823953</v>
+        <v>0.6630859341840921</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8216317214189375</v>
+        <v>0.6370744083830867</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8212927383680899</v>
+        <v>0.6363964422813918</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8248629071050622</v>
+        <v>0.6376250436226102</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7943231185686124</v>
+        <v>0.6180698527677957</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.7785476736179886</v>
+        <v>0.6085430519792875</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7632170378125501</v>
+        <v>0.6156871622195184</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7802073135074465</v>
+        <v>0.6138609546985088</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.760661931844977</v>
+        <v>0.6185205097007254</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7694402158022315</v>
+        <v>0.6150444714826029</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7625998132480688</v>
+        <v>0.5945938145496732</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7554772077756713</v>
+        <v>0.6253256368901088</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7616651104005734</v>
+        <v>0.5998157003669016</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7344642200277298</v>
+        <v>0.5628723956122729</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7350207030549976</v>
+        <v>0.5570195146336172</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7374641351404885</v>
+        <v>0.5516761457419617</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7365901738302066</v>
+        <v>0.5516761457419617</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5817496203653924</v>
+        <v>0.5423766541222188</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5987300868679437</v>
+        <v>0.5349993869254784</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5901947690595437</v>
+        <v>0.5359242805806287</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5733867179762882</v>
+        <v>0.5294581364420927</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5721268026748912</v>
+        <v>0.5197940069607538</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5334514209181027</v>
+        <v>0.5199547268045612</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5254510813691369</v>
+        <v>0.5126440489327787</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5370881789800327</v>
+        <v>0.5129830319836262</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5300597040264848</v>
+        <v>0.4965198117389623</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.542131801590221</v>
+        <v>0.4686054912613301</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.542131801590221</v>
+        <v>0.4686054912613301</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5584695773558568</v>
+        <v>0.466040576101412</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.567020552144346</v>
+        <v>0.4673965083048018</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5343195344406403</v>
+        <v>0.4663854069400036</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5356911236241193</v>
+        <v>0.4643201946747404</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5449455306867378</v>
+        <v>0.4712586891523537</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5449455306867378</v>
+        <v>0.4719973967912622</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5418594078643313</v>
+        <v>0.487106759853994</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5001018646897372</v>
+        <v>0.4809148958244909</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4998138139837582</v>
+        <v>0.4988066740235609</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5006426907369156</v>
+        <v>0.499903983098007</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5020593644775191</v>
+        <v>0.5006426907369156</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5012599153013969</v>
+        <v>0.4988870339454647</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.500981673787763</v>
+        <v>0.4988870339454647</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.500981673787763</v>
+        <v>0.4994435169727323</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5007034322741292</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4990339831923262</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4990339831923262</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4998687077332277</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4995904662195939</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
